--- a/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
+++ b/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M59"/>
+  <dimension ref="A1:M74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4299,9 +4299,939 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Choose folder &amp; settings</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>DDF-1, DDF-19</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/DeDupeSettings.cs (DeDupeSettingsStore)</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/DeDupeSettingsTests.cs</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L60" s="2">
+        <f>IF(COUNTA(D60,F60,G60,H60,I60,K60)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Recursive scan &amp; skip rules</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>DDF-2</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/ScanEngine.cs (Collect)</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/ScanEngineTests.cs</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L61" s="2">
+        <f>IF(COUNTA(D61,F61,G61,H61,I61,K61)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>MD5 checksum computation</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>DDF-3</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FileHasher.cs (Md5FileHasher, Compute)</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/FileHasherTests.cs</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L62" s="2">
+        <f>IF(COUNTA(D62,F62,G62,H62,I62,K62)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Checksum list file (read/write)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>DDF-4, DDF-5</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/ChecksumListFile.cs (Read, Write, ParseLine, FormatLine)</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/ChecksumListFileTests.cs</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L63" s="2">
+        <f>IF(COUNTA(D63,F63,G63,H63,I63,K63)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Incremental rescan &amp; pruning</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>DDF-6</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/ScanEngine.cs (Run), src/Features/DeDupeFiles/ChecksumEntry.cs (Matches)</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/ScanEngineTests.cs</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L64" s="2">
+        <f>IF(COUNTA(D64,F64,G64,H64,I64,K64)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>In-memory checksum index</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>DDF-7</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/ChecksumIndex.cs (Put, Find, RetainOnly, GroupByHash)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/ChecksumIndexTests.cs</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L65" s="2">
+        <f>IF(COUNTA(D65,F65,G65,H65,I65,K65)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate analysis &amp; savings</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>DDF-8, DDF-11</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/DuplicateAnalyzer.cs (Analyze)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/DuplicateAnalyzerTests.cs</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L66" s="2">
+        <f>IF(COUNTA(D66,F66,G66,H66,I66,K66)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Keeper selection policy</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>DDF-10</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/DuplicateAnalyzer.cs (PickKeeper)</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/DuplicateAnalyzerTests.cs</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L67" s="2">
+        <f>IF(COUNTA(D67,F67,G67,H67,I67,K67)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate list in the window</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>DDF-9</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/DeDupeFilesControl.cs (ShowDuplicates)</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>n/a (UI - covered by QA automation)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L68" s="2">
+        <f>IF(COUNTA(D68,F68,G68,H68,I68,K68)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Dry run &amp; confirmation</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>DDF-12</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/DeleteEngine.cs (Run), src/Features/DeDupeFiles/DeDupeFilesControl.cs (OnDelete)</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/DeleteEngineTests.cs</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L69" s="2">
+        <f>IF(COUNTA(D69,F69,G69,H69,I69,K69)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Byte-for-byte verification</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>DDF-13</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FileComparer.cs (AreIdentical)</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/FileComparerTests.cs</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L70" s="2">
+        <f>IF(COUNTA(D70,F70,G70,H70,I70,K70)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Recycle Bin / permanent delete</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>DDF-14</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/DeleteEngine.cs (PermanentFileDeleter, RecycleBinFileDeleter)</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/DeleteEngineTests.cs</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L71" s="2">
+        <f>IF(COUNTA(D71,F71,G71,H71,I71,K71)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Results summary &amp; report</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>DDF-15, DDF-18</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/DeDupeReportText.cs (Render), src/Features/DeDupeFiles/ByteSize.cs (Format)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/DeDupeReportTextTests.cs</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L72" s="2">
+        <f>IF(COUNTA(D72,F72,G72,H72,I72,K72)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Progress, pause &amp; resume</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>DDF-16</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/PauseToken.cs (Pause, Resume), src/Features/DeDupeFiles/DeDupeFilesControl.cs (OnPauseResume, OnStop)</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/PauseTokenTests.cs</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L73" s="2">
+        <f>IF(COUNTA(D73,F73,G73,H73,I73,K73)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>DeDupe Files</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Autosave / resumable scan</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>DDF-17</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/dedupe-files.md</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/dedupe-files.png</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/ScanEngine.cs (Run)</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/ScanEngineTests.cs</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#dedupe</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/DeDupeFiles/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L74" s="2">
+        <f>IF(COUNTA(D74,F74,G74,H74,I74,K74)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
-  <conditionalFormatting sqref="L2:L59">
+  <conditionalFormatting sqref="L2:L74">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("Gap",L2))</formula>
     </cfRule>

--- a/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
+++ b/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5229,9 +5229,815 @@
       </c>
       <c r="M74" s="2" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Choose folder &amp; settings</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>SST-1, SST-16</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/StorageSettings.cs (StorageSettingsStore)</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/StorageSettingsAndPaletteTests.cs</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L75" s="2">
+        <f>IF(COUNTA(D75,F75,G75,H75,I75,K75)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Read-only scan &amp; skip rules</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>SST-2, SST-13</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/SpaceScanner.cs (Run)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/SpaceScannerTests.cs</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L76" s="2">
+        <f>IF(COUNTA(D76,F76,G76,H76,I76,K76)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Size tree with rolled-up totals</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>SST-3</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/SpaceNode.cs (AddFile, AddFolder, SortBySize)</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/SpaceNodeTests.cs</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L77" s="2">
+        <f>IF(COUNTA(D77,F77,G77,H77,I77,K77)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>File type classification</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>SST-4, SST-7</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FileCategory.cs (FileTypeClassifier)</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/FileTypeClassifierTests.cs</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L78" s="2">
+        <f>IF(COUNTA(D78,F78,G78,H78,I78,K78)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Squarified size map layout</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>SST-4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/TreemapLayout.cs (Squarify, Build)</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/TreemapLayoutTests.cs</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L79" s="2">
+        <f>IF(COUNTA(D79,F79,G79,H79,I79,K79)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Size map drawing &amp; drill-down</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>SST-5, SST-6</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/TreemapControl.cs (OnMouseClick), src/Features/StorageStudio/StorageStudioControl.cs (SetFocus)</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L80" s="2">
+        <f>IF(COUNTA(D80,F80,G80,H80,I80,K80)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Space by type &amp; by age</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>SST-7, SST-8</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/SpaceAnalyzer.cs (ByType, ByAge)</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/SpaceAnalyzerTests.cs</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L81" s="2">
+        <f>IF(COUNTA(D81,F81,G81,H81,I81,K81)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Largest files &amp; folders</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>SST-9, SST-10</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/SpaceAnalyzer.cs (LargestFiles, LargestFolders)</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/SpaceAnalyzerTests.cs</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L82" s="2">
+        <f>IF(COUNTA(D82,F82,G82,H82,I82,K82)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Clean-up candidates</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>SST-11</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/CleanupFinder.cs (Find)</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/CleanupFinderTests.cs</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L83" s="2">
+        <f>IF(COUNTA(D83,F83,G83,H83,I83,K83)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Snapshot &amp; changes since last scan</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>SST-12</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/SpaceSnapshot.cs (SpaceSnapshot, GrowthComparer, SnapshotStore)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/SpaceSnapshotTests.cs</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L84" s="2">
+        <f>IF(COUNTA(D84,F84,G84,H84,I84,K84)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Explorer actions</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>SST-14</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/StorageStudioControl.cs (ShowNodeMenu)</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>n/a (UI - covered by QA automation)</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L85" s="2">
+        <f>IF(COUNTA(D85,F85,G85,H85,I85,K85)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Save report</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>SST-15</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/SpaceReportText.cs (Render)</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/SpaceReportTextTests.cs</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L86" s="2">
+        <f>IF(COUNTA(D86,F86,G86,H86,I86,K86)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Storage Studio</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Colour-blind-safe palette &amp; contrast</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>SST-17</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/storage-studio.md</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/storage-studio.png</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/CategoryPalette.cs (For, Fill, TextOn)</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/StorageStudio/StorageSettingsAndPaletteTests.cs</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#storage</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/StorageStudio/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L87" s="2">
+        <f>IF(COUNTA(D87,F87,G87,H87,I87,K87)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
-  <conditionalFormatting sqref="L2:L74">
+  <conditionalFormatting sqref="L2:L87">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("Gap",L2))</formula>
     </cfRule>

--- a/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
+++ b/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6035,9 +6035,815 @@
       </c>
       <c r="M87" s="2" t="inlineStr"/>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Choose folder &amp; settings</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>SIM-1</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/SimilarPicturesSettings.cs (SimilarPicturesSettingsStore)</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/ReportSettingsAndSampleTests.cs</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L88" s="2">
+        <f>IF(COUNTA(D88,F88,G88,H88,I88,K88)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Find pictures &amp; incremental cache</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>SIM-2, SIM-5, SIM-17</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/PictureScanner.cs (Collect, Run), src/Features/SimilarPictures/PictureRecord.cs (PictureCache)</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/PictureCacheAndScannerTests.cs</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L89" s="2">
+        <f>IF(COUNTA(D89,F89,G89,H89,I89,K89)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Read through Windows (Shell + GDI+)</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>SIM-3</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/PictureReader.cs (PictureReader, ShellThumbnailProvider, GdiThumbnailProvider)</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/PictureReaderTests.cs</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L90" s="2">
+        <f>IF(COUNTA(D90,F90,G90,H90,I90,K90)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Greyscale, resize, turn, sharpness</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>SIM-4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/GrayImage.cs (Resize, Transform, LaplacianVariance)</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/GrayImageTests.cs</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L91" s="2">
+        <f>IF(COUNTA(D91,F91,G91,H91,I91,K91)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Visual fingerprint (pHash + dHash)</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>SIM-4, SIM-7</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/ImageHasher.cs (Compute, PerceptualHash, DifferenceHash)</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/ImageHasherTests.cs</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L92" s="2">
+        <f>IF(COUNTA(D92,F92,G92,H92,I92,K92)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Matching, kinds &amp; sensitivity</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>SIM-6, SIM-7, SIM-8, SIM-9</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/SimilarityFinder.cs (Compare, DifferentMoments, Thresholds)</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/SimilarityFinderTests.cs</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L93" s="2">
+        <f>IF(COUNTA(D93,F93,G93,H93,I93,K93)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Grouping by keeper</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>SIM-11</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/SimilarityFinder.cs (Find)</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/SimilarityFinderTests.cs</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L94" s="2">
+        <f>IF(COUNTA(D94,F94,G94,H94,I94,K94)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Keeper choice</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>SIM-10</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/KeeperRanking.cs (Compare, LooksLikeCopy)</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/KeeperRankingTests.cs</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L95" s="2">
+        <f>IF(COUNTA(D95,F95,G95,H95,I95,K95)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Review screen &amp; manual verification</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>SIM-12, SIM-13</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/SimilarPicturesControl.cs (ShowGroup, MarkCurrent), src/Features/SimilarPictures/PictureCardControl.cs (SetMarked), src/Features/SimilarPictures/SamplePictureSet.cs (GroupEdits)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L96" s="2">
+        <f>IF(COUNTA(D96,F96,G96,H96,I96,K96)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Move to review folder / Recycle Bin</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>SIM-14, SIM-15</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/ReviewMover.cs (Plan, Run, TargetFor)</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/ReviewMoverTests.cs</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L97" s="2">
+        <f>IF(COUNTA(D97,F97,G97,H97,I97,K97)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Undo last move</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>SIM-16</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/ReviewMover.cs (Undo, SaveLastBatch, LoadLastBatch)</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/ReviewMoverTests.cs</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L98" s="2">
+        <f>IF(COUNTA(D98,F98,G98,H98,I98,K98)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>End-to-end: scan, group, move, undo</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>SIM-2, SIM-6, SIM-14, SIM-16</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/PictureScanner.cs (Run), src/Features/SimilarPictures/ReviewMover.cs (Run)</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/SimilarPicturesPipelineTests.cs</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L99" s="2">
+        <f>IF(COUNTA(D99,F99,G99,H99,I99,K99)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Similar Pictures</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Save report</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>SIM-18</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-pictures.md</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-pictures.png</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/SimilarReportText.cs (Render, Summary)</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/ReportSettingsAndSampleTests.cs</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#similar</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarPictures/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L100" s="2">
+        <f>IF(COUNTA(D100,F100,G100,H100,I100,K100)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
-  <conditionalFormatting sqref="L2:L87">
+  <conditionalFormatting sqref="L2:L100">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("Gap",L2))</formula>
     </cfRule>

--- a/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
+++ b/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
@@ -5071,7 +5071,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>src/Features/DeDupeFiles/DeDupeReportText.cs (Render), src/Features/DeDupeFiles/ByteSize.cs (Format)</t>
+          <t>src/Features/DeDupeFiles/DeDupeReportText.cs (Render), src/DigitalSecretary.Kit/ByteSize.cs (Format)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>src/Features/DeDupeFiles/PauseToken.cs (Pause, Resume), src/Features/DeDupeFiles/DeDupeFilesControl.cs (OnPauseResume, OnStop)</t>
+          <t>src/DigitalSecretary.Kit/PauseToken.cs (Pause, Resume), src/Features/DeDupeFiles/DeDupeFilesControl.cs (OnPauseResume, OnStop)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>tests/DigitalSecretary.UnitTests/Features/DeDupeFiles/PauseTokenTests.cs</t>
+          <t>tests/DigitalSecretary.UnitTests/Kit/PauseTokenTests.cs</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>src/Features/SimilarPictures/GrayImage.cs (Resize, Transform, LaplacianVariance)</t>
+          <t>src/DigitalSecretary.Kit/GrayImage.cs (Resize, Transform, LaplacianVariance)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>tests/DigitalSecretary.UnitTests/Features/SimilarPictures/GrayImageTests.cs</t>
+          <t>tests/DigitalSecretary.UnitTests/Kit/GrayImageTests.cs</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>src/Features/SimilarPictures/ImageHasher.cs (Compute, PerceptualHash, DifferenceHash)</t>
+          <t>src/DigitalSecretary.Kit/ImageHasher.cs (Compute, PerceptualHash, DifferenceHash)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>src/Features/SimilarPictures/ReviewMover.cs (Plan, Run, TargetFor)</t>
+          <t>src/Features/SimilarPictures/ReviewMover.cs (Plan, Run, TargetFor), src/DigitalSecretary.Kit/ReviewFolder.cs (Run, TargetFor)</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>src/Features/SimilarPictures/ReviewMover.cs (Undo, SaveLastBatch, LoadLastBatch)</t>
+          <t>src/Features/SimilarPictures/ReviewMover.cs (Undo, SaveLastBatch, LoadLastBatch), src/DigitalSecretary.Kit/ReviewFolder.cs (Undo, SaveLastBatch, LoadLastBatch)</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">

--- a/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
+++ b/docs/traceability/DigitalSecretary-Traceability-Matrix.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M100"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6841,9 +6841,699 @@
       </c>
       <c r="M100" s="2" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Choose folder &amp; settings</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>SVD-1</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-videos.png</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/SimilarVideosSettings.cs (SimilarVideosSettingsStore, ToFindOptions)</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarVideos/VideoReportSettingsAndSampleTests.cs</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#videos</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L101" s="2">
+        <f>IF(COUNTA(D101,F101,G101,H101,I101,K101)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Find videos, Live Photo rule &amp; incremental cache</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>SVD-2, SVD-3, SVD-6, SVD-19</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-videos.png</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/VideoScanner.cs (Collect, Run, IsLivePhotoCompanion), src/Features/SimilarVideos/VideoRecord.cs (VideoCache), src/DigitalSecretary.Kit/IncrementalScanner.cs (Collect, Run), src/DigitalSecretary.Kit/FileRecordCache.cs (FileRecordCache, CacheFiles)</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarVideos/VideoRecordAndScannerTests.cs</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#videos</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L102" s="2">
+        <f>IF(COUNTA(D102,F102,G102,H102,I102,K102)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Decode through Media Foundation</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>SVD-4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-videos.png</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/VideoDecoder.cs (Read, Filmstrip, ReaderSession, ViewOf), src/Features/SimilarVideos/MediaFoundation.cs (IMFSourceReader)</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarVideos/MediaFoundationRoundTripTests.cs</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#videos</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L103" s="2">
+        <f>IF(COUNTA(D103,F103,G103,H103,I103,K103)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>Integration: real MP4s encoded at test time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Frame fingerprints &amp; flat frames</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>SVD-5</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-videos.png</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/VideoRecord.cs (HashOf, From), src/Features/SimilarVideos/VideoDecoder.cs (ToGray, Upright)</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarVideos/VideoDecoderTests.cs</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#videos</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L104" s="2">
+        <f>IF(COUNTA(D104,F104,G104,H104,I104,K104)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Length gate, kinds &amp; sensitivity</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>SVD-7, SVD-8, SVD-9, SVD-10, SVD-11</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-videos.png</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/VideoMatcher.cs (Compare, DurationsAgree, VideoThresholds)</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarVideos/VideoMatcherTests.cs</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#videos</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L105" s="2">
+        <f>IF(COUNTA(D105,F105,G105,H105,I105,K105)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Grouping by keeper</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>SVD-12, SVD-13</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-videos.png</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/VideoMatcher.cs (Find), src/Features/SimilarVideos/VideoKeeperRanking.cs (Compare)</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarVideos/VideoKeeperAndMoverTests.cs</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#videos</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L106" s="2">
+        <f>IF(COUNTA(D106,F106,G106,H106,I106,K106)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Review screen &amp; manual verification</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>SVD-14, SVD-15</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-videos.png</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/SimilarVideosControl.cs (ShowGroup, MarkCurrent), src/Features/SimilarVideos/VideoCardControl.cs (SetMarked), src/Features/SimilarVideos/VideoReviewMover.cs (VideoGroupEdits)</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#videos</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L107" s="2">
+        <f>IF(COUNTA(D107,F107,G107,H107,I107,K107)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Move, Recycle Bin &amp; undo</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>SVD-16, SVD-17, SVD-18</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-videos.png</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/VideoReviewMover.cs (Plan, Run), src/DigitalSecretary.Kit/ReviewFolder.cs (Run, Undo, SaveLastBatch, LoadLastBatch)</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarVideos/VideoKeeperAndMoverTests.cs</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#videos</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L108" s="2">
+        <f>IF(COUNTA(D108,F108,G108,H108,I108,K108)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>End-to-end: scan, group, move, undo</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>SVD-2, SVD-8, SVD-16, SVD-18</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-videos.png</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/VideoScanner.cs (Run), src/Features/SimilarVideos/VideoReviewMover.cs (Run)</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarVideos/SimilarVideosPipelineTests.cs</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#videos</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L109" s="2">
+        <f>IF(COUNTA(D109,F109,G109,H109,I109,K109)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Similar Videos</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Save report</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>SVD-20</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>docs/requirements/features/similar-videos.md</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/images/similar-videos.png</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/VideoReportText.cs (Render, Summary, Duration)</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Features/SimilarVideos/VideoReportSettingsAndSampleTests.cs</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#videos</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>src/Features/SimilarVideos/FEATURE.md</t>
+        </is>
+      </c>
+      <c r="L110" s="2">
+        <f>IF(COUNTA(D110,F110,G110,H110,I110,K110)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Application Shell</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Shared helper kit (ENH-12)</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>NFR-6</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>src/DigitalSecretary.Kit/README.md</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>src/DigitalSecretary.Kit/FileNames.cs (LooksLikeCopy), src/DigitalSecretary.Kit/Ranking.cs (PreferLarger), src/DigitalSecretary.Kit/GrayImage.cs (StandardDeviation)</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.UnitTests/Kit/KitHelpersTests.cs</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>tests/DigitalSecretary.QaTests/PluginPipelineQaTests.cs (Feature_loads_instantiates_and_builds_a_view)</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>docs/user-guide/DigitalSecretary-User-Manual.html#start</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>docs/ARCHITECTURE.md (#isolation)</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>src/DigitalSecretary.Kit/README.md</t>
+        </is>
+      </c>
+      <c r="L111" s="2">
+        <f>IF(COUNTA(D111,F111,G111,H111,I111,K111)=6,"Complete","Gap - fill artifacts")</f>
+        <v/>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>Kit DLL ships inside each plugin that uses it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:M1"/>
-  <conditionalFormatting sqref="L2:L100">
+  <conditionalFormatting sqref="L2:L111">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("Gap",L2))</formula>
     </cfRule>
